--- a/JsonConverter/ExcelFiles/0_Character.xlsx
+++ b/JsonConverter/ExcelFiles/0_Character.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF7034D-DDDF-4E78-A60B-8FEB61DBB6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2DFBEF-46E9-4B76-BF67-F20574EB3FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14280" yWindow="2280" windowWidth="14385" windowHeight="14055" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Character" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>Id</t>
   </si>
@@ -43,16 +43,10 @@
     <t>캐릭터 전체 컨셉이나 스토리</t>
   </si>
   <si>
-    <t>character_Player_01</t>
-  </si>
-  <si>
     <t>게임 주인공이다.</t>
   </si>
   <si>
     <t>캐릭터 고유 ID</t>
-  </si>
-  <si>
-    <t>character_Minhyeong_01</t>
   </si>
   <si>
     <t>여 주인공이다.</t>
@@ -63,6 +57,22 @@
   </si>
   <si>
     <t>Description</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>민형</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Player_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Minhyeong_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -382,7 +392,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="9" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+    <tableStyle name="Normal Style 1 - Accent 1" pivot="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="13"/>
       <tableStyleElement type="headerRow" dxfId="12"/>
       <tableStyleElement type="totalRow" dxfId="11"/>
@@ -391,7 +401,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="8"/>
       <tableStyleElement type="firstColumnStripe" dxfId="7"/>
     </tableStyle>
-    <tableStyle name="Light Style 1 - Accent 1" table="0" count="8" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+    <tableStyle name="Light Style 1 - Accent 1" table="0" count="7" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -624,7 +634,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1" t="s">
@@ -653,21 +663,21 @@
         <v>4</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>5</v>
@@ -675,20 +685,22 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A6" s="4"/>
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>

--- a/JsonConverter/ExcelFiles/0_Character.xlsx
+++ b/JsonConverter/ExcelFiles/0_Character.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2DFBEF-46E9-4B76-BF67-F20574EB3FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E735A77E-05E6-477E-8858-039D67514F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -69,10 +69,6 @@
   </si>
   <si>
     <t>character_Minhyeong_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>character_Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -698,9 +694,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="A6" s="4"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
     </row>

--- a/JsonConverter/ExcelFiles/0_Character.xlsx
+++ b/JsonConverter/ExcelFiles/0_Character.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2DFBEF-46E9-4B76-BF67-F20574EB3FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A32C9E-7EC1-4023-8FD3-DC2866A759AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="1560" windowWidth="28185" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Character" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>Id</t>
   </si>
@@ -72,7 +72,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>character_Date</t>
+    <t>character_Hyunwoo_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>현우</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>교육을 같이 듣는 동료 이다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -80,7 +88,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -111,6 +119,13 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="8">
@@ -186,7 +201,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -209,6 +224,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -701,8 +717,15 @@
       <c r="A6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="3"/>

--- a/JsonConverter/ExcelFiles/0_Character.xlsx
+++ b/JsonConverter/ExcelFiles/0_Character.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A32C9E-7EC1-4023-8FD3-DC2866A759AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E848833-7D73-4070-A66F-2EF319085071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="1560" windowWidth="28185" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Character" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,6 @@
     <t>캐릭터 고유 ID</t>
   </si>
   <si>
-    <t>여 주인공이다.</t>
-  </si>
-  <si>
     <t>characterData</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -81,6 +78,10 @@
   </si>
   <si>
     <t>교육을 같이 듣는 동료 이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>여 주인공이다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -679,15 +680,15 @@
         <v>4</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>5</v>
@@ -701,13 +702,13 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>3</v>
@@ -715,16 +716,16 @@
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="D6" s="12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/0_Character.xlsx
+++ b/JsonConverter/ExcelFiles/0_Character.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E848833-7D73-4070-A66F-2EF319085071}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83A064A-F0B3-4F5F-B50D-BC124B559ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="870" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Character" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -82,6 +82,18 @@
   </si>
   <si>
     <t>여 주인공이다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>character_Jooyoung_01</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>누나</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>플레이어의 누나이다</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -729,9 +741,18 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="A7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="5"/>

--- a/JsonConverter/ExcelFiles/0_Character.xlsx
+++ b/JsonConverter/ExcelFiles/0_Character.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83A064A-F0B3-4F5F-B50D-BC124B559ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="870" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Character" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_Character.xlsx
+++ b/JsonConverter/ExcelFiles/0_Character.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83A064A-F0B3-4F5F-B50D-BC124B559ADF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE44DDA5-59B8-473B-8E86-ADCC6CEFE19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="870" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Character" sheetId="1" r:id="rId1"/>

--- a/JsonConverter/ExcelFiles/0_Character.xlsx
+++ b/JsonConverter/ExcelFiles/0_Character.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0_SonghaUnityGame\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE44DDA5-59B8-473B-8E86-ADCC6CEFE19B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2A20EF2-4094-4314-866B-D0790A7DF678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="870" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="615" yWindow="990" windowWidth="28185" windowHeight="14490" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_Character" sheetId="1" r:id="rId1"/>
